--- a/research/traditional_assets/database/data/norway/norway_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_semiconductor_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.125</v>
+        <v>-0.103</v>
       </c>
       <c r="G2">
-        <v>0.03970588235294118</v>
+        <v>-0.009404388714733543</v>
       </c>
       <c r="H2">
-        <v>0.02941176470588235</v>
+        <v>-0.01943573667711599</v>
       </c>
       <c r="I2">
-        <v>-0.2016132238350158</v>
+        <v>-0.2333476949590693</v>
       </c>
       <c r="J2">
-        <v>-0.2016132238350158</v>
+        <v>-0.2333476949590693</v>
       </c>
       <c r="K2">
-        <v>-43.6</v>
+        <v>-73.90000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.3205882352941177</v>
+        <v>-0.4633228840125392</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>126.3</v>
+        <v>146.8</v>
       </c>
       <c r="V2">
-        <v>0.1666446760786383</v>
+        <v>0.2458549656673924</v>
       </c>
       <c r="W2">
-        <v>2.270833333333333</v>
+        <v>-1.75952380952381</v>
       </c>
       <c r="X2">
-        <v>0.1082059315301747</v>
+        <v>0.184612386802239</v>
       </c>
       <c r="Y2">
-        <v>2.162627401803159</v>
+        <v>-1.944136196326049</v>
       </c>
       <c r="Z2">
-        <v>0.8227614924113156</v>
+        <v>1.40411373260738</v>
       </c>
       <c r="AA2">
-        <v>-0.1658795969323542</v>
+        <v>-0.3276467029643073</v>
       </c>
       <c r="AB2">
-        <v>0.09081015179764659</v>
+        <v>0.1510367794324095</v>
       </c>
       <c r="AC2">
-        <v>-0.2566897487300008</v>
+        <v>-0.4786834823967167</v>
       </c>
       <c r="AD2">
-        <v>197.8</v>
+        <v>185.3</v>
       </c>
       <c r="AE2">
-        <v>0.09699220781075019</v>
+        <v>0.09478672985781991</v>
       </c>
       <c r="AF2">
-        <v>197.8969922078108</v>
+        <v>185.3947867298578</v>
       </c>
       <c r="AG2">
-        <v>71.59699220781077</v>
+        <v>38.59478672985782</v>
       </c>
       <c r="AH2">
-        <v>0.2070491891282116</v>
+        <v>0.2369278235125955</v>
       </c>
       <c r="AI2">
-        <v>0.8249248579006047</v>
+        <v>0.6766361832739752</v>
       </c>
       <c r="AJ2">
-        <v>0.08631374541485239</v>
+        <v>0.0607127626897763</v>
       </c>
       <c r="AK2">
-        <v>0.6302719008337253</v>
+        <v>0.3034305707184935</v>
       </c>
       <c r="AL2">
-        <v>23.1</v>
+        <v>21.4</v>
       </c>
       <c r="AM2">
-        <v>22.9</v>
+        <v>20.4</v>
       </c>
       <c r="AN2">
-        <v>-109.8888888888889</v>
+        <v>-13.23571428571429</v>
       </c>
       <c r="AO2">
-        <v>-1.19047619047619</v>
+        <v>-1.742990654205608</v>
       </c>
       <c r="AP2">
-        <v>-39.7761067821171</v>
+        <v>-2.75677048070413</v>
       </c>
       <c r="AQ2">
-        <v>-1.200873362445415</v>
+        <v>-1.82843137254902</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.125</v>
+        <v>-0.103</v>
       </c>
       <c r="G3">
-        <v>0.03970588235294118</v>
+        <v>-0.009404388714733543</v>
       </c>
       <c r="H3">
-        <v>0.02941176470588235</v>
+        <v>-0.01943573667711599</v>
       </c>
       <c r="I3">
-        <v>-0.2016132238350158</v>
+        <v>-0.2333476949590693</v>
       </c>
       <c r="J3">
-        <v>-0.2016132238350158</v>
+        <v>-0.2333476949590693</v>
       </c>
       <c r="K3">
-        <v>-43.6</v>
+        <v>-73.90000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.3205882352941177</v>
+        <v>-0.4633228840125392</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>126.3</v>
+        <v>146.8</v>
       </c>
       <c r="V3">
-        <v>0.1666446760786383</v>
+        <v>0.2458549656673924</v>
       </c>
       <c r="W3">
-        <v>2.270833333333333</v>
+        <v>-1.75952380952381</v>
       </c>
       <c r="X3">
-        <v>0.1082059315301747</v>
+        <v>0.184612386802239</v>
       </c>
       <c r="Y3">
-        <v>2.162627401803159</v>
+        <v>-1.944136196326049</v>
       </c>
       <c r="Z3">
-        <v>0.8227614924113156</v>
+        <v>1.40411373260738</v>
       </c>
       <c r="AA3">
-        <v>-0.1658795969323542</v>
+        <v>-0.3276467029643073</v>
       </c>
       <c r="AB3">
-        <v>0.09081015179764659</v>
+        <v>0.1510367794324095</v>
       </c>
       <c r="AC3">
-        <v>-0.2566897487300008</v>
+        <v>-0.4786834823967167</v>
       </c>
       <c r="AD3">
-        <v>197.8</v>
+        <v>185.3</v>
       </c>
       <c r="AE3">
-        <v>0.09699220781075019</v>
+        <v>0.09478672985781991</v>
       </c>
       <c r="AF3">
-        <v>197.8969922078108</v>
+        <v>185.3947867298578</v>
       </c>
       <c r="AG3">
-        <v>71.59699220781077</v>
+        <v>38.59478672985782</v>
       </c>
       <c r="AH3">
-        <v>0.2070491891282116</v>
+        <v>0.2369278235125955</v>
       </c>
       <c r="AI3">
-        <v>0.8249248579006047</v>
+        <v>0.6766361832739752</v>
       </c>
       <c r="AJ3">
-        <v>0.08631374541485239</v>
+        <v>0.0607127626897763</v>
       </c>
       <c r="AK3">
-        <v>0.6302719008337253</v>
+        <v>0.3034305707184935</v>
       </c>
       <c r="AL3">
-        <v>23.1</v>
+        <v>21.4</v>
       </c>
       <c r="AM3">
-        <v>22.9</v>
+        <v>20.4</v>
       </c>
       <c r="AN3">
-        <v>-109.8888888888889</v>
+        <v>-13.23571428571429</v>
       </c>
       <c r="AO3">
-        <v>-1.19047619047619</v>
+        <v>-1.742990654205608</v>
       </c>
       <c r="AP3">
-        <v>-39.7761067821171</v>
+        <v>-2.75677048070413</v>
       </c>
       <c r="AQ3">
-        <v>-1.200873362445415</v>
+        <v>-1.82843137254902</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_semiconductor_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.103</v>
+        <v>-0.12</v>
       </c>
       <c r="G2">
-        <v>-0.009404388714733543</v>
+        <v>-0.2692889561270802</v>
       </c>
       <c r="H2">
-        <v>-0.01943573667711599</v>
+        <v>-0.2836611195158851</v>
       </c>
       <c r="I2">
-        <v>-0.2333476949590693</v>
+        <v>-0.6552120432788427</v>
       </c>
       <c r="J2">
-        <v>-0.2333476949590693</v>
+        <v>-0.6552120432788427</v>
       </c>
       <c r="K2">
-        <v>-73.90000000000001</v>
+        <v>-99.90000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.4633228840125392</v>
+        <v>-0.7556732223903178</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>146.8</v>
+        <v>121.7</v>
       </c>
       <c r="V2">
-        <v>0.2458549656673924</v>
+        <v>0.2095746512829344</v>
       </c>
       <c r="W2">
-        <v>-1.75952380952381</v>
+        <v>-1.127539503386005</v>
       </c>
       <c r="X2">
-        <v>0.184612386802239</v>
+        <v>0.17220394406543</v>
       </c>
       <c r="Y2">
-        <v>-1.944136196326049</v>
+        <v>-1.299743447451435</v>
       </c>
       <c r="Z2">
-        <v>1.40411373260738</v>
+        <v>1.039347718645808</v>
       </c>
       <c r="AA2">
-        <v>-0.3276467029643073</v>
+        <v>-0.6809931424111239</v>
       </c>
       <c r="AB2">
-        <v>0.1510367794324095</v>
+        <v>0.1221584977470846</v>
       </c>
       <c r="AC2">
-        <v>-0.4786834823967167</v>
+        <v>-0.8031516401582084</v>
       </c>
       <c r="AD2">
-        <v>185.3</v>
+        <v>352.2</v>
       </c>
       <c r="AE2">
-        <v>0.09478672985781991</v>
+        <v>0.09516060731499588</v>
       </c>
       <c r="AF2">
-        <v>185.3947867298578</v>
+        <v>352.295160607315</v>
       </c>
       <c r="AG2">
-        <v>38.59478672985782</v>
+        <v>230.595160607315</v>
       </c>
       <c r="AH2">
-        <v>0.2369278235125955</v>
+        <v>0.3775959141931619</v>
       </c>
       <c r="AI2">
-        <v>0.6766361832739752</v>
+        <v>1.036481837452007</v>
       </c>
       <c r="AJ2">
-        <v>0.0607127626897763</v>
+        <v>0.2842309085570008</v>
       </c>
       <c r="AK2">
-        <v>0.3034305707184935</v>
+        <v>1.056829858029327</v>
       </c>
       <c r="AL2">
-        <v>21.4</v>
+        <v>17.2</v>
       </c>
       <c r="AM2">
-        <v>20.4</v>
+        <v>13.9</v>
       </c>
       <c r="AN2">
-        <v>-13.23571428571429</v>
+        <v>-4.671087533156498</v>
       </c>
       <c r="AO2">
-        <v>-1.742990654205608</v>
+        <v>-5.040697674418605</v>
       </c>
       <c r="AP2">
-        <v>-2.75677048070413</v>
+        <v>-3.058291254738926</v>
       </c>
       <c r="AQ2">
-        <v>-1.82843137254902</v>
+        <v>-6.237410071942447</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.103</v>
+        <v>-0.12</v>
       </c>
       <c r="G3">
-        <v>-0.009404388714733543</v>
+        <v>-0.2692889561270802</v>
       </c>
       <c r="H3">
-        <v>-0.01943573667711599</v>
+        <v>-0.2836611195158851</v>
       </c>
       <c r="I3">
-        <v>-0.2333476949590693</v>
+        <v>-0.6552120432788427</v>
       </c>
       <c r="J3">
-        <v>-0.2333476949590693</v>
+        <v>-0.6552120432788427</v>
       </c>
       <c r="K3">
-        <v>-73.90000000000001</v>
+        <v>-99.90000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.4633228840125392</v>
+        <v>-0.7556732223903178</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>146.8</v>
+        <v>121.7</v>
       </c>
       <c r="V3">
-        <v>0.2458549656673924</v>
+        <v>0.2095746512829344</v>
       </c>
       <c r="W3">
-        <v>-1.75952380952381</v>
+        <v>-1.127539503386005</v>
       </c>
       <c r="X3">
-        <v>0.184612386802239</v>
+        <v>0.17220394406543</v>
       </c>
       <c r="Y3">
-        <v>-1.944136196326049</v>
+        <v>-1.299743447451435</v>
       </c>
       <c r="Z3">
-        <v>1.40411373260738</v>
+        <v>1.039347718645808</v>
       </c>
       <c r="AA3">
-        <v>-0.3276467029643073</v>
+        <v>-0.6809931424111239</v>
       </c>
       <c r="AB3">
-        <v>0.1510367794324095</v>
+        <v>0.1221584977470846</v>
       </c>
       <c r="AC3">
-        <v>-0.4786834823967167</v>
+        <v>-0.8031516401582084</v>
       </c>
       <c r="AD3">
-        <v>185.3</v>
+        <v>352.2</v>
       </c>
       <c r="AE3">
-        <v>0.09478672985781991</v>
+        <v>0.09516060731499588</v>
       </c>
       <c r="AF3">
-        <v>185.3947867298578</v>
+        <v>352.295160607315</v>
       </c>
       <c r="AG3">
-        <v>38.59478672985782</v>
+        <v>230.595160607315</v>
       </c>
       <c r="AH3">
-        <v>0.2369278235125955</v>
+        <v>0.3775959141931619</v>
       </c>
       <c r="AI3">
-        <v>0.6766361832739752</v>
+        <v>1.036481837452007</v>
       </c>
       <c r="AJ3">
-        <v>0.0607127626897763</v>
+        <v>0.2842309085570008</v>
       </c>
       <c r="AK3">
-        <v>0.3034305707184935</v>
+        <v>1.056829858029327</v>
       </c>
       <c r="AL3">
-        <v>21.4</v>
+        <v>17.2</v>
       </c>
       <c r="AM3">
-        <v>20.4</v>
+        <v>13.9</v>
       </c>
       <c r="AN3">
-        <v>-13.23571428571429</v>
+        <v>-4.671087533156498</v>
       </c>
       <c r="AO3">
-        <v>-1.742990654205608</v>
+        <v>-5.040697674418605</v>
       </c>
       <c r="AP3">
-        <v>-2.75677048070413</v>
+        <v>-3.058291254738926</v>
       </c>
       <c r="AQ3">
-        <v>-1.82843137254902</v>
+        <v>-6.237410071942447</v>
       </c>
     </row>
   </sheetData>
